--- a/section-b/programs/ecommerce.xlsx
+++ b/section-b/programs/ecommerce.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\kaushalya\consultancy\nhce\2026\nhce\mba\powerbi\workshop\section-b\programs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A411C1AF-6520-4C3E-983C-2F62D1029907}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83BE8B2F-EB59-4FC2-BE91-23CA7A8C21D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{F22B3850-3CB8-47F4-8B65-A73239C6EC0C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F22B3850-3CB8-47F4-8B65-A73239C6EC0C}"/>
   </bookViews>
   <sheets>
     <sheet name="customer" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -108,6 +108,12 @@
   </si>
   <si>
     <t>qty</t>
+  </si>
+  <si>
+    <t>name3</t>
+  </si>
+  <si>
+    <t>name4</t>
   </si>
 </sst>
 </file>
@@ -471,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5CD5441-2D55-4F59-97FD-1CA8AF146566}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.109375" bestFit="1" customWidth="1"/>
@@ -530,10 +536,46 @@
         <v>9845547472</v>
       </c>
     </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>9845547472</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>9845547472</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{AA6701E9-C908-45B4-A4FA-1240292E45B9}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{ECC61947-B6A3-4CEE-957C-812BE883001B}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{9574FF54-C759-4E91-B84E-5EC99BB6A4AB}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{FAC8F794-C82D-49AA-B5D9-8229821A1238}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
